--- a/antigen_CI_Random_generator.xlsx
+++ b/antigen_CI_Random_generator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="11_4A5645C871AEA98286DE389EAFF8EF0F542BC54D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBC65D6F-7301-4708-8E29-B33A7B960330}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="11_4A5645C871AEA98286DE389EAFF8EF0F542BC54D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{031EF5AB-3623-4B22-9D9E-9B6362BDB60A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diphtheria" sheetId="1" r:id="rId1"/>
@@ -333,34 +333,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>327232858.03333443</c:v>
+                  <c:v>668711630.97059476</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>649944236.34959435</c:v>
+                  <c:v>480616326.09376627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>560302998.90472198</c:v>
+                  <c:v>919869439.18637204</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1042625820.562032</c:v>
+                  <c:v>441785696.17447162</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>510588894.16854215</c:v>
+                  <c:v>1175631224.0320301</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>479167335.02357817</c:v>
+                  <c:v>1118697127.1032255</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>976065417.33206522</c:v>
+                  <c:v>222801394.26304269</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1321623604.6141024</c:v>
+                  <c:v>1276991560.3171983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>879952390.0379113</c:v>
+                  <c:v>958027381.63566697</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1197020211.462297</c:v>
+                  <c:v>910991680.46485686</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -405,34 +405,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>30566966.94629205</c:v>
+                  <c:v>39449727.696229212</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29027711.288915388</c:v>
+                  <c:v>39171087.503391333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32270669.644030765</c:v>
+                  <c:v>43213295.37544775</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5946849.4759663558</c:v>
+                  <c:v>12760586.391169745</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37483032.037034526</c:v>
+                  <c:v>32225757.429372102</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>42021681.512458093</c:v>
+                  <c:v>41628011.463997461</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34544390.715838939</c:v>
+                  <c:v>10996818.081699103</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70179578.126479328</c:v>
+                  <c:v>83158666.06054008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54616437.796520501</c:v>
+                  <c:v>35959899.251897521</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>59994176.318614952</c:v>
+                  <c:v>53834405.459043458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -477,34 +477,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>354205415.20987809</c:v>
+                  <c:v>560668762.91228616</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>236954804.18550211</c:v>
+                  <c:v>622720654.02015126</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>616159579.41819811</c:v>
+                  <c:v>279775088.51454234</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>580507730.72273779</c:v>
+                  <c:v>464102163.95118344</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>303527153.47317624</c:v>
+                  <c:v>267192583.28856084</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>732016026.1027863</c:v>
+                  <c:v>377747003.04040194</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>594427335.00427151</c:v>
+                  <c:v>868007275.7718246</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>684905075.0431416</c:v>
+                  <c:v>548428672.59601927</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>667175195.82137167</c:v>
+                  <c:v>744078980.27370739</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>850171021.21135867</c:v>
+                  <c:v>668638613.28303933</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -549,34 +549,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>545886518.23867655</c:v>
+                  <c:v>598235125.39881134</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>654796722.74096465</c:v>
+                  <c:v>589594066.71965468</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>472845159.87652242</c:v>
+                  <c:v>665158233.16738868</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>709805108.61953497</c:v>
+                  <c:v>437709524.92591959</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>830070687.12944019</c:v>
+                  <c:v>752956555.26537728</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1700247205.047471</c:v>
+                  <c:v>1273811402.3870955</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1127085574.637809</c:v>
+                  <c:v>1204076319.1870573</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1606166862.0387561</c:v>
+                  <c:v>711570368.59967816</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1246392508.9811087</c:v>
+                  <c:v>2104607163.3171096</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2036109357.9502878</c:v>
+                  <c:v>1812401882.5088484</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -621,34 +621,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>570605073.91759527</c:v>
+                  <c:v>603736982.98584616</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>752572987.22965991</c:v>
+                  <c:v>665105809.78212726</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>677117498.94918931</c:v>
+                  <c:v>531869164.81250584</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>627117517.05473673</c:v>
+                  <c:v>642846709.18160868</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>614532678.69396663</c:v>
+                  <c:v>783299591.19648957</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>633721558.16306436</c:v>
+                  <c:v>744451221.43771935</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>695026996.93511546</c:v>
+                  <c:v>586927124.45508289</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>684598607.43860519</c:v>
+                  <c:v>702196359.33043039</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>693760728.96945417</c:v>
+                  <c:v>543903873.54236531</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>735345049.6186341</c:v>
+                  <c:v>689224887.66142046</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -693,34 +693,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>345850274.94382304</c:v>
+                  <c:v>346625883.55871749</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>351306495.40975714</c:v>
+                  <c:v>353018316.42575198</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>349286088.21975571</c:v>
+                  <c:v>301127887.5331828</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>348203704.08028978</c:v>
+                  <c:v>342500003.51635331</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>418909703.87263548</c:v>
+                  <c:v>326092899.74651456</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>387509863.47427124</c:v>
+                  <c:v>321979738.07856309</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>401779528.58627391</c:v>
+                  <c:v>386570534.91374749</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>289684556.48208266</c:v>
+                  <c:v>392793259.90781736</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>378599943.87861127</c:v>
+                  <c:v>429799466.91357923</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>339110933.25407159</c:v>
+                  <c:v>424178075.46458918</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -767,34 +767,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>449867903.82097661</c:v>
+                  <c:v>414981029.01353019</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>336859309.44006526</c:v>
+                  <c:v>443149074.98348886</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>354261939.02673423</c:v>
+                  <c:v>435305781.56504625</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>378203754.33729917</c:v>
+                  <c:v>578326531.38370085</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>462984899.28802919</c:v>
+                  <c:v>356257579.80316103</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>421022891.9110744</c:v>
+                  <c:v>469243838.26145369</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>496862154.47590828</c:v>
+                  <c:v>209388573.52115196</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>691898223.90495968</c:v>
+                  <c:v>334398604.43727034</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>466214837.88700908</c:v>
+                  <c:v>542415889.9338336</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>410560287.75263631</c:v>
+                  <c:v>343515728.07024628</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -841,34 +841,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>314892480.85949016</c:v>
+                  <c:v>286821612.53156221</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>362352073.69339001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>385843061.42481089</c:v>
+                  <c:v>320477253.98425764</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>374305696.21362072</c:v>
+                  <c:v>325677127.65123475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>269938022.25210083</c:v>
+                  <c:v>315963946.45239854</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>401638846.53089845</c:v>
+                  <c:v>402928044.19322556</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>333449511.40092641</c:v>
+                  <c:v>363483551.79338175</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>405959606.50779802</c:v>
+                  <c:v>369318949.92487359</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>419800670.41925281</c:v>
+                  <c:v>386821314.01674855</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>345731100.20960015</c:v>
+                  <c:v>432800370.53421861</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -918,31 +918,31 @@
                   <c:v>716469135.2208643</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>657974309.62493527</c:v>
+                  <c:v>783694552.35479057</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>525451510.27095741</c:v>
+                  <c:v>694558018.42390716</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>589525368.07691526</c:v>
+                  <c:v>519253104.41226047</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>825200441.98331952</c:v>
+                  <c:v>846545769.72766078</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>546877499.18765593</c:v>
+                  <c:v>874902965.92980409</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>789554193.32267201</c:v>
+                  <c:v>951023429.01607442</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>787211889.24952233</c:v>
+                  <c:v>915624691.61749613</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1120368516.7528012</c:v>
+                  <c:v>1038325781.1518395</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>679667475.8336184</c:v>
+                  <c:v>898968400.15119553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -989,34 +989,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>31963266.345840931</c:v>
+                  <c:v>25915770.51731832</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>39307452.706052743</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38250600.375207432</c:v>
+                  <c:v>35258738.193920977</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>48122185.881140113</c:v>
+                  <c:v>39200401.038449273</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47653519.512356326</c:v>
+                  <c:v>47265943.538656689</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61292965.407283232</c:v>
+                  <c:v>59430649.707607023</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>78042264.65959689</c:v>
+                  <c:v>64565628.185461171</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>74149519.026301503</c:v>
+                  <c:v>76221504.649861902</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81327848.355241328</c:v>
+                  <c:v>76400904.950654998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>96041229.237888366</c:v>
+                  <c:v>92858989.55012843</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1063,34 +1063,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>151905241.58038071</c:v>
+                  <c:v>239577204.00124341</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>184158506.34682065</c:v>
+                  <c:v>269501978.84332263</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>114045264.6782148</c:v>
+                  <c:v>286864851.98515236</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>345071647.16502643</c:v>
+                  <c:v>136881744.54928535</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>220278680.87787583</c:v>
+                  <c:v>218169265.00123906</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>446059995.10940337</c:v>
+                  <c:v>335530973.63952714</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>256427774.78029674</c:v>
+                  <c:v>281247690.38399482</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>413848784.27904564</c:v>
+                  <c:v>316967212.40048289</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>543185133.04546654</c:v>
+                  <c:v>896373650.61798525</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>542245098.33165169</c:v>
+                  <c:v>694368986.98709249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1140,31 +1140,31 @@
                   <c:v>211403260.01881739</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>299613342.8843587</c:v>
+                  <c:v>303936532.15251517</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>363423456.81929737</c:v>
+                  <c:v>200898755.51546949</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>431025210.27462173</c:v>
+                  <c:v>407327762.47830319</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>374903871.96941876</c:v>
+                  <c:v>237877147.95639929</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>315754043.89689839</c:v>
+                  <c:v>439507439.59369993</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>671941120.10131812</c:v>
+                  <c:v>166480198.96793035</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>411655009.81450933</c:v>
+                  <c:v>415297688.68271244</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>509524028.94588882</c:v>
+                  <c:v>664164889.69489038</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>648953792.91621602</c:v>
+                  <c:v>327661585.79673731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2964,43 +2964,43 @@
       </c>
       <c r="B2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D2,Measles!$F$13)</f>
-        <v>327232858.03333443</v>
+        <v>1011577036.3664331</v>
       </c>
       <c r="C2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D3,Measles!$F$13)</f>
-        <v>649944236.34959435</v>
+        <v>480616326.09376627</v>
       </c>
       <c r="D2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D4,Measles!$F$13)</f>
-        <v>560302998.90472198</v>
+        <v>1184487529.4737849</v>
       </c>
       <c r="E2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D5,Measles!$F$13)</f>
-        <v>1264474654.9508467</v>
+        <v>441785696.17447162</v>
       </c>
       <c r="F2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D6,Measles!$F$13)</f>
-        <v>510588894.16854215</v>
+        <v>1222204360.0146823</v>
       </c>
       <c r="G2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D7,Measles!$F$13)</f>
-        <v>479167335.02357817</v>
+        <v>1118697127.1032255</v>
       </c>
       <c r="H2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D8,Measles!$F$13)</f>
-        <v>976065417.33206522</v>
+        <v>222801394.26304269</v>
       </c>
       <c r="I2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D9,Measles!$F$13)</f>
-        <v>1321623604.6141024</v>
+        <v>1276991560.3171983</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D10,Measles!$F$13)</f>
-        <v>879952390.0379113</v>
+        <v>958027381.63566697</v>
       </c>
       <c r="K2" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Measles!$D11,Measles!$F$13)</f>
-        <v>1197020211.462297</v>
+        <v>910991680.46485686</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -3009,43 +3009,43 @@
       </c>
       <c r="B3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D2,Mumps!$F$13)</f>
-        <v>30566966.94629205</v>
+        <v>66130645.139304034</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D3,Mumps!$F$13)</f>
-        <v>29027711.288915388</v>
+        <v>39171087.503391333</v>
       </c>
       <c r="D3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D4,Mumps!$F$13)</f>
-        <v>32270669.644030765</v>
+        <v>43213295.37544775</v>
       </c>
       <c r="E3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D5,Mumps!$F$13)</f>
-        <v>4526348.6193893775</v>
+        <v>12760586.391169745</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D6,Mumps!$F$13)</f>
-        <v>37483032.037034526</v>
+        <v>32225757.429372102</v>
       </c>
       <c r="G3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D7,Mumps!$F$13)</f>
-        <v>42021681.512458093</v>
+        <v>41628011.463997461</v>
       </c>
       <c r="H3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D8,Mumps!$F$13)</f>
-        <v>34544390.715838939</v>
+        <v>10996818.081699103</v>
       </c>
       <c r="I3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D9,Mumps!$F$13)</f>
-        <v>70179578.126479328</v>
+        <v>83158666.06054008</v>
       </c>
       <c r="J3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D10,Mumps!$F$13)</f>
-        <v>54616437.796520501</v>
+        <v>35959899.251897521</v>
       </c>
       <c r="K3" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Mumps!$D11,Mumps!$F$13)</f>
-        <v>59994176.318614952</v>
+        <v>53834405.459043458</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3054,43 +3054,43 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D2,Rubella!$F$13)</f>
-        <v>354205415.20987809</v>
+        <v>599495459.42354751</v>
       </c>
       <c r="C4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D3,Rubella!$F$13)</f>
-        <v>236954804.18550211</v>
+        <v>622720654.02015126</v>
       </c>
       <c r="D4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D4,Rubella!$F$13)</f>
-        <v>616159579.41819811</v>
+        <v>279775088.51454234</v>
       </c>
       <c r="E4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D5,Rubella!$F$13)</f>
-        <v>580507730.72273779</v>
+        <v>464102163.95118344</v>
       </c>
       <c r="F4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D6,Rubella!$F$13)</f>
-        <v>303527153.47317624</v>
+        <v>267192583.28856084</v>
       </c>
       <c r="G4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D7,Rubella!$F$13)</f>
-        <v>732016026.1027863</v>
+        <v>377747003.04040194</v>
       </c>
       <c r="H4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D8,Rubella!$F$13)</f>
-        <v>594427335.00427151</v>
+        <v>868007275.7718246</v>
       </c>
       <c r="I4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D9,Rubella!$F$13)</f>
-        <v>684905075.0431416</v>
+        <v>548428672.59601927</v>
       </c>
       <c r="J4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D10,Rubella!$F$13)</f>
-        <v>667175195.82137167</v>
+        <v>744078980.27370739</v>
       </c>
       <c r="K4" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rubella!$D11,Rubella!$F$13)</f>
-        <v>850171021.21135867</v>
+        <v>668638613.28303933</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3099,43 +3099,43 @@
       </c>
       <c r="B5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D2,Diphtheria!$F$13)</f>
-        <v>285756801.16792679</v>
+        <v>598235125.39881134</v>
       </c>
       <c r="C5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D3,Diphtheria!$F$13)</f>
-        <v>654796722.74096465</v>
+        <v>589594066.71965468</v>
       </c>
       <c r="D5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D4,Diphtheria!$F$13)</f>
-        <v>443540455.95709848</v>
+        <v>665158233.16738868</v>
       </c>
       <c r="E5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D5,Diphtheria!$F$13)</f>
-        <v>709805108.61953497</v>
+        <v>-283262378.70910633</v>
       </c>
       <c r="F5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D6,Diphtheria!$F$13)</f>
-        <v>830070687.12944019</v>
+        <v>752956555.26537728</v>
       </c>
       <c r="G5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D8,Diphtheria!$F$13)</f>
-        <v>1730562276.7648411</v>
+        <v>1273811402.3870955</v>
       </c>
       <c r="H5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D9,Diphtheria!$F$13)</f>
-        <v>1127085574.637809</v>
+        <v>1204076319.1870573</v>
       </c>
       <c r="I5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D10,Diphtheria!$F$13)</f>
-        <v>1606166862.0387561</v>
+        <v>711570368.59967816</v>
       </c>
       <c r="J5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D10,Diphtheria!$F$13)</f>
-        <v>1246392508.9811087</v>
+        <v>2104607163.3171096</v>
       </c>
       <c r="K5" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Diphtheria!$D11,Diphtheria!$F$13)</f>
-        <v>2036109357.9502878</v>
+        <v>1812401882.5088484</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -3144,43 +3144,43 @@
       </c>
       <c r="B6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D2,Tetanus!$F$13)</f>
-        <v>389671648.55273438</v>
+        <v>603736982.98584616</v>
       </c>
       <c r="C6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D3,Tetanus!$F$13)</f>
-        <v>853453478.34760988</v>
+        <v>665105809.78212726</v>
       </c>
       <c r="D6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D4,Tetanus!$F$13)</f>
-        <v>677117498.94918931</v>
+        <v>531869164.81250584</v>
       </c>
       <c r="E6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D5,Tetanus!$F$13)</f>
-        <v>627117517.05473673</v>
+        <v>642846709.18160868</v>
       </c>
       <c r="F6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D6,Tetanus!$F$13)</f>
-        <v>614532678.69396663</v>
+        <v>783299591.19648957</v>
       </c>
       <c r="G6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D7,Tetanus!$F$13)</f>
-        <v>633721558.16306436</v>
+        <v>744451221.43771935</v>
       </c>
       <c r="H6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D8,Tetanus!$F$13)</f>
-        <v>695026996.93511546</v>
+        <v>586927124.45508289</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D9,Tetanus!$F$13)</f>
-        <v>684598607.43860519</v>
+        <v>702196359.33043039</v>
       </c>
       <c r="J6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D10,Tetanus!$F$13)</f>
-        <v>693760728.96945417</v>
+        <v>543903873.54236531</v>
       </c>
       <c r="K6" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Tetanus!$D11,Tetanus!$F$13)</f>
-        <v>735345049.6186341</v>
+        <v>689224887.66142046</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -3189,43 +3189,43 @@
       </c>
       <c r="B7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D2,Pertussis!$F$13)</f>
-        <v>345850274.94382304</v>
+        <v>346625883.55871749</v>
       </c>
       <c r="C7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D2,Pertussis!$F$13)</f>
-        <v>351306495.40975714</v>
+        <v>353018316.42575198</v>
       </c>
       <c r="D7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D4,Pertussis!$F$13)</f>
-        <v>349286088.21975571</v>
+        <v>301127887.5331828</v>
       </c>
       <c r="E7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D5,Pertussis!$F$13)</f>
-        <v>348203704.08028978</v>
+        <v>342500003.51635331</v>
       </c>
       <c r="F7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D6,Pertussis!$F$13)</f>
-        <v>418909703.87263548</v>
+        <v>326092899.74651456</v>
       </c>
       <c r="G7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D7,Pertussis!$F$13)</f>
-        <v>387509863.47427124</v>
+        <v>321979738.07856309</v>
       </c>
       <c r="H7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D8,Pertussis!$F$13)</f>
-        <v>401779528.58627391</v>
+        <v>386570534.91374749</v>
       </c>
       <c r="I7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D9,Pertussis!$F$13)</f>
-        <v>289684556.48208266</v>
+        <v>392793259.90781736</v>
       </c>
       <c r="J7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D10,Pertussis!$F$13)</f>
-        <v>378599943.87861127</v>
+        <v>429799466.91357923</v>
       </c>
       <c r="K7" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Pertussis!$D11,Pertussis!$F$13)</f>
-        <v>339110933.25407159</v>
+        <v>424178075.46458918</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -3234,43 +3234,43 @@
       </c>
       <c r="B8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D2,Hepatitis_B!$F$13)</f>
-        <v>525169381.61697102</v>
+        <v>414981029.01353019</v>
       </c>
       <c r="C8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D3,Hepatitis_B!$F$13)</f>
-        <v>336859309.44006526</v>
+        <v>443149074.98348886</v>
       </c>
       <c r="D8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D4,Hepatitis_B!$F$13)</f>
-        <v>354261939.02673423</v>
+        <v>435305781.56504625</v>
       </c>
       <c r="E8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D5,Hepatitis_B!$F$13)</f>
-        <v>378203754.33729917</v>
+        <v>578326531.38370085</v>
       </c>
       <c r="F8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D6,Hepatitis_B!$F$13)</f>
-        <v>462984899.28802919</v>
+        <v>356257579.80316103</v>
       </c>
       <c r="G8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D7,Hepatitis_B!$F$13)</f>
-        <v>421022891.9110744</v>
+        <v>469243838.26145369</v>
       </c>
       <c r="H8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D8,Hepatitis_B!$F$13)</f>
-        <v>496862154.47590828</v>
+        <v>209388573.52115196</v>
       </c>
       <c r="I8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D9,Hepatitis_B!$F$13)</f>
-        <v>691898223.90495968</v>
+        <v>334398604.43727034</v>
       </c>
       <c r="J8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D10,Hepatitis_B!$F$13)</f>
-        <v>466214837.88700908</v>
+        <v>542415889.9338336</v>
       </c>
       <c r="K8" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D11,Hepatitis_B!$F$13)</f>
-        <v>410560287.75263631</v>
+        <v>343515728.07024628</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -3279,43 +3279,43 @@
       </c>
       <c r="B9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D2,Hib!$F$13)</f>
-        <v>314892480.85949016</v>
+        <v>286821612.53156221</v>
       </c>
       <c r="C9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D3,Hib!$F$13)</f>
-        <v>373753724.56387347</v>
+        <v>420922549.82869357</v>
       </c>
       <c r="D9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D4,Hib!$F$13)</f>
-        <v>414428216.90577292</v>
+        <v>320477253.98425764</v>
       </c>
       <c r="E9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D5,Hib!$F$13)</f>
-        <v>374305696.21362072</v>
+        <v>325677127.65123475</v>
       </c>
       <c r="F9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D6,Hib!$F$13)</f>
-        <v>269938022.25210083</v>
+        <v>315963946.45239854</v>
       </c>
       <c r="G9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D7,Hib!$F$13)</f>
-        <v>401638846.53089845</v>
+        <v>402928044.19322556</v>
       </c>
       <c r="H9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D8,Hib!$F$13)</f>
-        <v>333449511.40092641</v>
+        <v>363483551.79338175</v>
       </c>
       <c r="I9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D9,Hib!$F$13)</f>
-        <v>405959606.50779802</v>
+        <v>369318949.92487359</v>
       </c>
       <c r="J9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D10,Hib!$F$13)</f>
-        <v>419800670.41925281</v>
+        <v>386821314.01674855</v>
       </c>
       <c r="K9" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hib!$D11,Hib!$F$13)</f>
-        <v>345731100.20960015</v>
+        <v>432800370.53421861</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -3324,43 +3324,43 @@
       </c>
       <c r="B10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D2,Polio!$F$13)</f>
-        <v>780887703.11928654</v>
+        <v>774152406.91967511</v>
       </c>
       <c r="C10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D3,Polio!$F$13)</f>
-        <v>657974309.62493527</v>
+        <v>792596057.30054009</v>
       </c>
       <c r="D10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D4,Polio!$F$13)</f>
-        <v>390813543.28725153</v>
+        <v>694558018.42390716</v>
       </c>
       <c r="E10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D5,Polio!$F$13)</f>
-        <v>589525368.07691526</v>
+        <v>494828052.42929089</v>
       </c>
       <c r="F10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D6,Polio!$F$13)</f>
-        <v>825200441.98331952</v>
+        <v>846545769.72766078</v>
       </c>
       <c r="G10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D7,Polio!$F$13)</f>
-        <v>546877499.18765593</v>
+        <v>874902965.92980409</v>
       </c>
       <c r="H10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D8,Polio!$F$13)</f>
-        <v>789554193.32267201</v>
+        <v>951023429.01607442</v>
       </c>
       <c r="I10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D9,Polio!$F$13)</f>
-        <v>787211889.24952233</v>
+        <v>915624691.61749613</v>
       </c>
       <c r="J10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D10,Polio!$F$13)</f>
-        <v>1120368516.7528012</v>
+        <v>1038325781.1518395</v>
       </c>
       <c r="K10" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Polio!$D11,Polio!$F$13)</f>
-        <v>679667475.8336184</v>
+        <v>898968400.15119553</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -3369,43 +3369,43 @@
       </c>
       <c r="B11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D2,HPV!$F$13)</f>
-        <v>35010959.237957411</v>
+        <v>22707286.07624644</v>
       </c>
       <c r="C11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D3,HPV!$F$13)</f>
-        <v>40083367.200387515</v>
+        <v>42342950.293604173</v>
       </c>
       <c r="D11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D4,HPV!$F$13)</f>
-        <v>38250600.375207432</v>
+        <v>33780255.922059357</v>
       </c>
       <c r="E11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D5,HPV!$F$13)</f>
-        <v>48122185.881140113</v>
+        <v>36791008.936819799</v>
       </c>
       <c r="F11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D6,HPV!$F$13)</f>
-        <v>47653519.512356326</v>
+        <v>47265943.538656689</v>
       </c>
       <c r="G11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D7,HPV!$F$13)</f>
-        <v>61292965.407283232</v>
+        <v>59430649.707607023</v>
       </c>
       <c r="H11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D8,HPV!$F$13)</f>
-        <v>78042264.65959689</v>
+        <v>64565628.185461171</v>
       </c>
       <c r="I11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D9,HPV!$F$13)</f>
-        <v>74149519.026301503</v>
+        <v>76221504.649861902</v>
       </c>
       <c r="J11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D10,HPV!$F$13)</f>
-        <v>81327848.355241328</v>
+        <v>76400904.950654998</v>
       </c>
       <c r="K11" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),HPV!$D11,HPV!$F$13)</f>
-        <v>96041229.237888366</v>
+        <v>92858989.55012843</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -3414,43 +3414,43 @@
       </c>
       <c r="B12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D2,Rotavirus!$F$13)</f>
-        <v>-79432639.848430216</v>
+        <v>366845486.35103482</v>
       </c>
       <c r="C12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D3,Rotavirus!$F$13)</f>
-        <v>184158506.34682065</v>
+        <v>269501978.84332263</v>
       </c>
       <c r="D12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D4,Rotavirus!$F$13)</f>
-        <v>76757840.314862043</v>
+        <v>286864851.98515236</v>
       </c>
       <c r="E12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D5,Rotavirus!$F$13)</f>
-        <v>345071647.16502643</v>
+        <v>136881744.54928535</v>
       </c>
       <c r="F12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D6,Rotavirus!$F$13)</f>
-        <v>220278680.87787583</v>
+        <v>218169265.00123906</v>
       </c>
       <c r="G12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D7,Rotavirus!$F$13)</f>
-        <v>446059995.10940337</v>
+        <v>335530973.63952714</v>
       </c>
       <c r="H12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D8,Rotavirus!$F$13)</f>
-        <v>256427774.78029674</v>
+        <v>281247690.38399482</v>
       </c>
       <c r="I12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D9,Rotavirus!$F$13)</f>
-        <v>413848784.27904564</v>
+        <v>316967212.40048289</v>
       </c>
       <c r="J12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D10,Rotavirus!$F$13)</f>
-        <v>543185133.04546654</v>
+        <v>896373650.61798525</v>
       </c>
       <c r="K12" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Rotavirus!$D11,Rotavirus!$F$13)</f>
-        <v>542245098.33165169</v>
+        <v>694368986.98709249</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -3459,43 +3459,43 @@
       </c>
       <c r="B13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D2,PCV!$F$13)</f>
-        <v>78344908.491983622</v>
+        <v>182275970.58963406</v>
       </c>
       <c r="C13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D3,PCV!$F$13)</f>
-        <v>299613342.8843587</v>
+        <v>361916778.4410643</v>
       </c>
       <c r="D13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D4,PCV!$F$13)</f>
-        <v>386057331.42783689</v>
+        <v>1760593.1570278406</v>
       </c>
       <c r="E13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D5,PCV!$F$13)</f>
-        <v>495453687.25461262</v>
+        <v>407327762.47830319</v>
       </c>
       <c r="F13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D6,PCV!$F$13)</f>
-        <v>374903871.96941876</v>
+        <v>237877147.95639929</v>
       </c>
       <c r="G13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D7,PCV!$F$13)</f>
-        <v>315754043.89689839</v>
+        <v>439507439.59369993</v>
       </c>
       <c r="H13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D8,PCV!$F$13)</f>
-        <v>671941120.10131812</v>
+        <v>166480198.96793035</v>
       </c>
       <c r="I13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D9,PCV!$F$13)</f>
-        <v>411655009.81450933</v>
+        <v>415297688.68271244</v>
       </c>
       <c r="J13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),PCV!$D10,PCV!$F$13)</f>
-        <v>509524028.94588882</v>
+        <v>664164889.69489038</v>
       </c>
       <c r="K13" s="4">
         <f ca="1">_xlfn.NORM.INV(RAND(),Hepatitis_B!$D11,PCV!$F$13)</f>
-        <v>648953792.91621602</v>
+        <v>327661585.79673731</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -3504,43 +3504,43 @@
       </c>
       <c r="B15" s="7">
         <f ca="1">IF(B2&gt;Measles!B2,Measles!B2,IF(Scenario_data!B2 &lt;Measles!A2,Measles!A2,Scenario_data!B2))</f>
-        <v>327232858.03333443</v>
+        <v>668711630.97059476</v>
       </c>
       <c r="C15" s="7">
         <f ca="1">IF(C2&gt;Measles!B3,Measles!B3,IF(Scenario_data!C2 &lt;Measles!A3,Measles!A3,Scenario_data!C2))</f>
-        <v>649944236.34959435</v>
+        <v>480616326.09376627</v>
       </c>
       <c r="D15" s="7">
         <f ca="1">IF(D2&gt;Measles!B4,Measles!B4,IF(Scenario_data!D2 &lt;Measles!A4,Measles!A4,Scenario_data!D2))</f>
-        <v>560302998.90472198</v>
+        <v>919869439.18637204</v>
       </c>
       <c r="E15" s="7">
         <f ca="1">IF(E2&gt;Measles!B5,Measles!B5,IF(Scenario_data!E2 &lt;Measles!A5,Measles!A5,Scenario_data!E2))</f>
-        <v>1042625820.562032</v>
+        <v>441785696.17447162</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">IF(F2&gt;Measles!B6,Measles!B6,IF(Scenario_data!F2 &lt;Measles!A6,Measles!A6,Scenario_data!F2))</f>
-        <v>510588894.16854215</v>
+        <v>1175631224.0320301</v>
       </c>
       <c r="G15" s="7">
         <f ca="1">IF(G2&gt;Measles!B7,Measles!B7,IF(Scenario_data!G2 &lt;Measles!A7,Measles!A7,Scenario_data!G2))</f>
-        <v>479167335.02357817</v>
+        <v>1118697127.1032255</v>
       </c>
       <c r="H15" s="7">
         <f ca="1">IF(H2&gt;Measles!B8,Measles!B8,IF(Scenario_data!H2 &lt;Measles!A8,Measles!A8,Scenario_data!H2))</f>
-        <v>976065417.33206522</v>
+        <v>222801394.26304269</v>
       </c>
       <c r="I15" s="7">
         <f ca="1">IF(I2&gt;Measles!B9,Measles!B9,IF(Scenario_data!I2 &lt;Measles!A9,Measles!A9,Scenario_data!I2))</f>
-        <v>1321623604.6141024</v>
+        <v>1276991560.3171983</v>
       </c>
       <c r="J15" s="7">
         <f ca="1">IF(J2&gt;Measles!B10,Measles!B10,IF(Scenario_data!J2 &lt;Measles!A10,Measles!A10,Scenario_data!J2))</f>
-        <v>879952390.0379113</v>
+        <v>958027381.63566697</v>
       </c>
       <c r="K15" s="7">
         <f ca="1">IF(K2&gt;Measles!B11,Measles!B11,IF(Scenario_data!K2 &lt;Measles!A11,Measles!A11,Scenario_data!K2))</f>
-        <v>1197020211.462297</v>
+        <v>910991680.46485686</v>
       </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -3551,43 +3551,43 @@
       </c>
       <c r="B16" s="7">
         <f ca="1">IF(B3&gt;Mumps!B2,Mumps!B2,IF(Scenario_data!B3 &lt;Mumps!A2,Mumps!A2,Scenario_data!B3))</f>
-        <v>30566966.94629205</v>
+        <v>39449727.696229212</v>
       </c>
       <c r="C16" s="7">
         <f ca="1">IF(C3&gt;Mumps!B3,Mumps!B3,IF(Scenario_data!C3 &lt;Mumps!A3,Mumps!A3,Scenario_data!C3))</f>
-        <v>29027711.288915388</v>
+        <v>39171087.503391333</v>
       </c>
       <c r="D16" s="7">
         <f ca="1">IF(D3&gt;Mumps!B4,Mumps!B4,IF(Scenario_data!D3 &lt;Mumps!A4,Mumps!A4,Scenario_data!D3))</f>
-        <v>32270669.644030765</v>
+        <v>43213295.37544775</v>
       </c>
       <c r="E16" s="7">
         <f ca="1">IF(E3&gt;Mumps!B5,Mumps!B5,IF(Scenario_data!E3 &lt;Mumps!A5,Mumps!A5,Scenario_data!E3))</f>
-        <v>5946849.4759663558</v>
+        <v>12760586.391169745</v>
       </c>
       <c r="F16" s="7">
         <f ca="1">IF(F3&gt;Mumps!B6,Mumps!B6,IF(Scenario_data!F3 &lt;Mumps!A6,Mumps!A6,Scenario_data!F3))</f>
-        <v>37483032.037034526</v>
+        <v>32225757.429372102</v>
       </c>
       <c r="G16" s="7">
         <f ca="1">IF(G3&gt;Mumps!B7,Mumps!B7,IF(Scenario_data!G3 &lt;Mumps!A7,Mumps!A7,Scenario_data!G3))</f>
-        <v>42021681.512458093</v>
+        <v>41628011.463997461</v>
       </c>
       <c r="H16" s="7">
         <f ca="1">IF(H3&gt;Mumps!B8,Mumps!B8,IF(Scenario_data!H3 &lt;Mumps!A8,Mumps!A8,Scenario_data!H3))</f>
-        <v>34544390.715838939</v>
+        <v>10996818.081699103</v>
       </c>
       <c r="I16" s="7">
         <f ca="1">IF(I3&gt;Mumps!B9,Mumps!B9,IF(Scenario_data!I3 &lt;Mumps!A9,Mumps!A9,Scenario_data!I3))</f>
-        <v>70179578.126479328</v>
+        <v>83158666.06054008</v>
       </c>
       <c r="J16" s="7">
         <f ca="1">IF(J3&gt;Mumps!B10,Mumps!B10,IF(Scenario_data!J3 &lt;Mumps!A10,Mumps!A10,Scenario_data!J3))</f>
-        <v>54616437.796520501</v>
+        <v>35959899.251897521</v>
       </c>
       <c r="K16" s="7">
         <f ca="1">IF(K3&gt;Mumps!B11,Mumps!B11,IF(Scenario_data!K3 &lt;Mumps!A11,Mumps!A11,Scenario_data!K3))</f>
-        <v>59994176.318614952</v>
+        <v>53834405.459043458</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -3596,43 +3596,43 @@
       </c>
       <c r="B17" s="7">
         <f ca="1">IF(B4&gt;Rubella!B2,Rubella!B2,IF(Scenario_data!B4 &lt;Rubella!A2,Rubella!A2,Scenario_data!B4))</f>
-        <v>354205415.20987809</v>
+        <v>560668762.91228616</v>
       </c>
       <c r="C17" s="7">
         <f ca="1">IF(C4&gt;Rubella!B3,Rubella!B3,IF(Scenario_data!C4 &lt;Rubella!A3,Rubella!A3,Scenario_data!C4))</f>
-        <v>236954804.18550211</v>
+        <v>622720654.02015126</v>
       </c>
       <c r="D17" s="7">
         <f ca="1">IF(D4&gt;Rubella!B4,Rubella!B4,IF(Scenario_data!D4 &lt;Rubella!A4,Rubella!A4,Scenario_data!D4))</f>
-        <v>616159579.41819811</v>
+        <v>279775088.51454234</v>
       </c>
       <c r="E17" s="7">
         <f ca="1">IF(E4&gt;Rubella!B5,Rubella!B5,IF(Scenario_data!E4 &lt;Rubella!A5,Rubella!A5,Scenario_data!E4))</f>
-        <v>580507730.72273779</v>
+        <v>464102163.95118344</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">IF(F4&gt;Rubella!B6,Rubella!B6,IF(Scenario_data!F4 &lt;Rubella!A6,Rubella!A6,Scenario_data!F4))</f>
-        <v>303527153.47317624</v>
+        <v>267192583.28856084</v>
       </c>
       <c r="G17" s="7">
         <f ca="1">IF(G4&gt;Rubella!B7,Rubella!B7,IF(Scenario_data!G4 &lt;Rubella!A7,Rubella!A7,Scenario_data!G4))</f>
-        <v>732016026.1027863</v>
+        <v>377747003.04040194</v>
       </c>
       <c r="H17" s="7">
         <f ca="1">IF(H4&gt;Rubella!B8,Rubella!B8,IF(Scenario_data!H4 &lt;Rubella!A8,Rubella!A8,Scenario_data!H4))</f>
-        <v>594427335.00427151</v>
+        <v>868007275.7718246</v>
       </c>
       <c r="I17" s="7">
         <f ca="1">IF(I4&gt;Rubella!B9,Rubella!B9,IF(Scenario_data!I4 &lt;Rubella!A9,Rubella!A9,Scenario_data!I4))</f>
-        <v>684905075.0431416</v>
+        <v>548428672.59601927</v>
       </c>
       <c r="J17" s="7">
         <f ca="1">IF(J4&gt;Rubella!B10,Rubella!B10,IF(Scenario_data!J4 &lt;Rubella!A10,Rubella!A10,Scenario_data!J4))</f>
-        <v>667175195.82137167</v>
+        <v>744078980.27370739</v>
       </c>
       <c r="K17" s="7">
         <f ca="1">IF(K4&gt;Rubella!B12=1,Rubella!B11,IF(Scenario_data!K4 &lt;Rubella!A11,Rubella!A11,Scenario_data!K4))</f>
-        <v>850171021.21135867</v>
+        <v>668638613.28303933</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -3641,43 +3641,43 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">IF(B5&gt;Diphtheria!B2,Diphtheria!B2,IF(Scenario_data!B5 &lt;Diphtheria!A2,Diphtheria!A2,Scenario_data!B5))</f>
-        <v>545886518.23867655</v>
+        <v>598235125.39881134</v>
       </c>
       <c r="C18" s="7">
         <f ca="1">IF(C5&gt;Diphtheria!B3,Diphtheria!B3,IF(Scenario_data!C5 &lt;Diphtheria!A3,Diphtheria!A3,Scenario_data!C5))</f>
-        <v>654796722.74096465</v>
+        <v>589594066.71965468</v>
       </c>
       <c r="D18" s="7">
         <f ca="1">IF(D5&gt;Diphtheria!B4,Diphtheria!B4,IF(Scenario_data!D5 &lt;Diphtheria!A4,Diphtheria!A4,Scenario_data!D5))</f>
-        <v>472845159.87652242</v>
+        <v>665158233.16738868</v>
       </c>
       <c r="E18" s="7">
         <f ca="1">IF(E5&gt;Diphtheria!B5,Diphtheria!B5,IF(Scenario_data!E5 &lt;Diphtheria!A5,Diphtheria!A5,Scenario_data!E5))</f>
-        <v>709805108.61953497</v>
+        <v>437709524.92591959</v>
       </c>
       <c r="F18" s="7">
         <f ca="1">IF(F5&gt;Diphtheria!B6,Diphtheria!B6,IF(Scenario_data!F5 &lt;Diphtheria!A6,Diphtheria!A6,Scenario_data!F5))</f>
-        <v>830070687.12944019</v>
+        <v>752956555.26537728</v>
       </c>
       <c r="G18" s="7">
         <f ca="1">IF(G5&gt;Diphtheria!B7,Diphtheria!B7,IF(Scenario_data!G5 &lt;Diphtheria!A7,Diphtheria!A7,Scenario_data!G5))</f>
-        <v>1700247205.047471</v>
+        <v>1273811402.3870955</v>
       </c>
       <c r="H18" s="7">
         <f ca="1">IF(H5&gt;Diphtheria!B8,Diphtheria!B8,IF(Scenario_data!H5 &lt;Diphtheria!A8,Diphtheria!A8,Scenario_data!H5))</f>
-        <v>1127085574.637809</v>
+        <v>1204076319.1870573</v>
       </c>
       <c r="I18" s="7">
         <f ca="1">IF(I5&gt;Diphtheria!B9,Diphtheria!B9,IF(Scenario_data!I5 &lt;Diphtheria!A9,Diphtheria!A9,Scenario_data!I5))</f>
-        <v>1606166862.0387561</v>
+        <v>711570368.59967816</v>
       </c>
       <c r="J18" s="7">
         <f ca="1">IF(J5&gt;Diphtheria!B10,Diphtheria!B10,IF(Scenario_data!J5 &lt;Diphtheria!A10,Diphtheria!A10,Scenario_data!J5))</f>
-        <v>1246392508.9811087</v>
+        <v>2104607163.3171096</v>
       </c>
       <c r="K18" s="7">
         <f ca="1">IF(K5&gt;Diphtheria!B11,Diphtheria!B11,IF(Scenario_data!K5 &lt;Diphtheria!A11,Diphtheria!A11,Scenario_data!K5))</f>
-        <v>2036109357.9502878</v>
+        <v>1812401882.5088484</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -3686,43 +3686,43 @@
       </c>
       <c r="B19" s="7">
         <f ca="1">IF(B6&gt;Tetanus!B2,Tetanus!B2,IF(Scenario_data!B6 &lt;Tetanus!A2,Tetanus!A2,Scenario_data!B6))</f>
-        <v>570605073.91759527</v>
+        <v>603736982.98584616</v>
       </c>
       <c r="C19" s="7">
         <f ca="1">IF(C6&gt;Tetanus!B3,Tetanus!B3,IF(Scenario_data!C6 &lt;Tetanus!A3,Tetanus!A3,Scenario_data!C6))</f>
-        <v>752572987.22965991</v>
+        <v>665105809.78212726</v>
       </c>
       <c r="D19" s="7">
         <f ca="1">IF(D6&gt;Tetanus!B4,Tetanus!B4,IF(Scenario_data!D6 &lt;Tetanus!A4,Tetanus!A4,Scenario_data!D6))</f>
-        <v>677117498.94918931</v>
+        <v>531869164.81250584</v>
       </c>
       <c r="E19" s="7">
         <f ca="1">IF(E6&gt;Tetanus!B5,Tetanus!B5,IF(Scenario_data!E6 &lt;Tetanus!A5,Tetanus!A5,Scenario_data!E6))</f>
-        <v>627117517.05473673</v>
+        <v>642846709.18160868</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">IF(F6&gt;Tetanus!B6,Tetanus!B6,IF(Scenario_data!F6 &lt;Tetanus!A6,Tetanus!A6,Scenario_data!F6))</f>
-        <v>614532678.69396663</v>
+        <v>783299591.19648957</v>
       </c>
       <c r="G19" s="7">
         <f ca="1">IF(G6&gt;Tetanus!B7,Tetanus!B7,IF(Scenario_data!G6 &lt;Tetanus!A7,Tetanus!A7,Scenario_data!G6))</f>
-        <v>633721558.16306436</v>
+        <v>744451221.43771935</v>
       </c>
       <c r="H19" s="7">
         <f ca="1">IF(H6&gt;Tetanus!B8,Tetanus!B8,IF(Scenario_data!H6 &lt;Tetanus!A8,Tetanus!A8,Scenario_data!H6))</f>
-        <v>695026996.93511546</v>
+        <v>586927124.45508289</v>
       </c>
       <c r="I19" s="7">
         <f ca="1">IF(I6&gt;Tetanus!B9,Tetanus!B9,IF(Scenario_data!I6 &lt;Tetanus!A9,Tetanus!A9,Scenario_data!I6))</f>
-        <v>684598607.43860519</v>
+        <v>702196359.33043039</v>
       </c>
       <c r="J19" s="7">
         <f ca="1">IF(J6&gt;Tetanus!B10,Tetanus!B10,IF(Scenario_data!J6 &lt;Tetanus!A10,Tetanus!A10,Scenario_data!J6))</f>
-        <v>693760728.96945417</v>
+        <v>543903873.54236531</v>
       </c>
       <c r="K19" s="7">
         <f ca="1">IF(K6&gt;Tetanus!B11,Tetanus!B11,IF(Scenario_data!K6 &lt;Tetanus!A11,Tetanus!A11,Scenario_data!K6))</f>
-        <v>735345049.6186341</v>
+        <v>689224887.66142046</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -3731,43 +3731,43 @@
       </c>
       <c r="B20" s="7">
         <f ca="1">IF(B7&gt;Pertussis!B2,Pertussis!B2,IF(Scenario_data!B7 &lt;Pertussis!A2,Pertussis!A2,Scenario_data!B7))</f>
-        <v>345850274.94382304</v>
+        <v>346625883.55871749</v>
       </c>
       <c r="C20" s="7">
         <f ca="1">IF(C7&gt;Pertussis!B3,Pertussis!B3,IF(Scenario_data!C7 &lt;Pertussis!A3,Pertussis!A3,Scenario_data!C7))</f>
-        <v>351306495.40975714</v>
+        <v>353018316.42575198</v>
       </c>
       <c r="D20" s="7">
         <f ca="1">IF(D7&gt;Pertussis!B4,Pertussis!B4,IF(Scenario_data!D7 &lt;Pertussis!A4,Pertussis!A4,Scenario_data!D7))</f>
-        <v>349286088.21975571</v>
+        <v>301127887.5331828</v>
       </c>
       <c r="E20" s="7">
         <f ca="1">IF(E7&gt;Pertussis!B5,Pertussis!B5,IF(Scenario_data!E7 &lt;Pertussis!A5,Pertussis!A5,Scenario_data!E7))</f>
-        <v>348203704.08028978</v>
+        <v>342500003.51635331</v>
       </c>
       <c r="F20" s="7">
         <f ca="1">IF(F7&gt;Pertussis!B6,Pertussis!B6,IF(Scenario_data!F7 &lt;Pertussis!A6,Pertussis!A6,Scenario_data!F7))</f>
-        <v>418909703.87263548</v>
+        <v>326092899.74651456</v>
       </c>
       <c r="G20" s="7">
         <f ca="1">IF(G7&gt;Pertussis!B7,Pertussis!B7,IF(Scenario_data!G7 &lt;Pertussis!A7,Pertussis!A7,Scenario_data!G7))</f>
-        <v>387509863.47427124</v>
+        <v>321979738.07856309</v>
       </c>
       <c r="H20" s="7">
         <f ca="1">IF(H7&gt;Pertussis!B8,Pertussis!B8,IF(Scenario_data!H7 &lt;Pertussis!A8,Pertussis!A8,Scenario_data!H7))</f>
-        <v>401779528.58627391</v>
+        <v>386570534.91374749</v>
       </c>
       <c r="I20" s="7">
         <f ca="1">IF(I7&gt;Pertussis!B9,Pertussis!B9,IF(Scenario_data!I7 &lt;Pertussis!A9,Pertussis!A9,Scenario_data!I7))</f>
-        <v>289684556.48208266</v>
+        <v>392793259.90781736</v>
       </c>
       <c r="J20" s="7">
         <f ca="1">IF(J7&gt;Pertussis!B10,Pertussis!B10,IF(Scenario_data!J7 &lt;Pertussis!A10,Pertussis!A10,Scenario_data!J7))</f>
-        <v>378599943.87861127</v>
+        <v>429799466.91357923</v>
       </c>
       <c r="K20" s="7">
         <f ca="1">IF(K7&gt;Pertussis!B11,Pertussis!B11,IF(Scenario_data!K7 &lt;Pertussis!A11,Pertussis!A11,Scenario_data!K7))</f>
-        <v>339110933.25407159</v>
+        <v>424178075.46458918</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -3776,43 +3776,43 @@
       </c>
       <c r="B21" s="7">
         <f ca="1">IF(B8&gt;Hepatitis_B!B2,Hepatitis_B!B2,IF(Scenario_data!B8 &lt;Hepatitis_B!A2,Hepatitis_B!A2,Scenario_data!B8))</f>
-        <v>449867903.82097661</v>
+        <v>414981029.01353019</v>
       </c>
       <c r="C21" s="7">
         <f ca="1">IF(C8&gt;Hepatitis_B!B3,Hepatitis_B!B3,IF(Scenario_data!C8 &lt;Hepatitis_B!A3,Hepatitis_B!A3,Scenario_data!C8))</f>
-        <v>336859309.44006526</v>
+        <v>443149074.98348886</v>
       </c>
       <c r="D21" s="7">
         <f ca="1">IF(D8&gt;Hepatitis_B!B4,Hepatitis_B!B4,IF(Scenario_data!D8 &lt;Hepatitis_B!A4,Hepatitis_B!A4,Scenario_data!D8))</f>
-        <v>354261939.02673423</v>
+        <v>435305781.56504625</v>
       </c>
       <c r="E21" s="7">
         <f ca="1">IF(E8&gt;Hepatitis_B!B5,Hepatitis_B!B5,IF(Scenario_data!E8 &lt;Hepatitis_B!A5,Hepatitis_B!A5,Scenario_data!E8))</f>
-        <v>378203754.33729917</v>
+        <v>578326531.38370085</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">IF(F8&gt;Hepatitis_B!B6,Hepatitis_B!B6,IF(Scenario_data!F8 &lt;Hepatitis_B!A6,Hepatitis_B!A6,Scenario_data!F8))</f>
-        <v>462984899.28802919</v>
+        <v>356257579.80316103</v>
       </c>
       <c r="G21" s="7">
         <f ca="1">IF(G8&gt;Hepatitis_B!B7,Hepatitis_B!B7,IF(Scenario_data!G8 &lt;Hepatitis_B!A7,Hepatitis_B!A7,Scenario_data!G8))</f>
-        <v>421022891.9110744</v>
+        <v>469243838.26145369</v>
       </c>
       <c r="H21" s="7">
         <f ca="1">IF(H8&gt;Hepatitis_B!B8,Hepatitis_B!B8,IF(Scenario_data!H8 &lt;Hepatitis_B!A8,Hepatitis_B!A8,Scenario_data!H8))</f>
-        <v>496862154.47590828</v>
+        <v>209388573.52115196</v>
       </c>
       <c r="I21" s="7">
         <f ca="1">IF(I8&gt;Hepatitis_B!B9,Hepatitis_B!B9,IF(Scenario_data!I8 &lt;Hepatitis_B!A9,Hepatitis_B!A9,Scenario_data!I8))</f>
-        <v>691898223.90495968</v>
+        <v>334398604.43727034</v>
       </c>
       <c r="J21" s="7">
         <f ca="1">IF(J8&gt;Hepatitis_B!B10,Hepatitis_B!B10,IF(Scenario_data!J8 &lt;Hepatitis_B!A10,Hepatitis_B!A10,Scenario_data!J8))</f>
-        <v>466214837.88700908</v>
+        <v>542415889.9338336</v>
       </c>
       <c r="K21" s="7">
         <f ca="1">IF(K8&gt;Hepatitis_B!B11,Hepatitis_B!B11,IF(Scenario_data!K8 &lt;Hepatitis_B!A11,Hepatitis_B!A11,Scenario_data!K8))</f>
-        <v>410560287.75263631</v>
+        <v>343515728.07024628</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B22" s="7">
         <f ca="1">IF(B9&gt;Hib!B2,Hib!B2,IF(Scenario_data!B9 &lt;Hib!A2,Hib!A2,Scenario_data!B9))</f>
-        <v>314892480.85949016</v>
+        <v>286821612.53156221</v>
       </c>
       <c r="C22" s="7">
         <f ca="1">IF(C9&gt;Hib!B3,Hib!B3,IF(Scenario_data!C9 &lt;Hib!A3,Hib!A3,Scenario_data!C9))</f>
@@ -3829,35 +3829,35 @@
       </c>
       <c r="D22" s="7">
         <f ca="1">IF(D9&gt;Hib!B4,Hib!B4,IF(Scenario_data!D9 &lt;Hib!A4,Hib!A4,Scenario_data!D9))</f>
-        <v>385843061.42481089</v>
+        <v>320477253.98425764</v>
       </c>
       <c r="E22" s="7">
         <f ca="1">IF(E9&gt;Hib!B5,Hib!B5,IF(Scenario_data!E9 &lt;Hib!A5,Hib!A5,Scenario_data!E9))</f>
-        <v>374305696.21362072</v>
+        <v>325677127.65123475</v>
       </c>
       <c r="F22" s="7">
         <f ca="1">IF(F9&gt;Hib!B6,Hib!B6,IF(Scenario_data!F9 &lt;Hib!A6,Hib!A6,Scenario_data!F9))</f>
-        <v>269938022.25210083</v>
+        <v>315963946.45239854</v>
       </c>
       <c r="G22" s="7">
         <f ca="1">IF(G9&gt;Hib!B7,Hib!B7,IF(Scenario_data!G9 &lt;Hib!A7,Hib!A7,Scenario_data!G9))</f>
-        <v>401638846.53089845</v>
+        <v>402928044.19322556</v>
       </c>
       <c r="H22" s="7">
         <f ca="1">IF(H9&gt;Hib!B8,Hib!B8,IF(Scenario_data!H9 &lt;Hib!A8,Hib!A8,Scenario_data!H9))</f>
-        <v>333449511.40092641</v>
+        <v>363483551.79338175</v>
       </c>
       <c r="I22" s="7">
         <f ca="1">IF(I9&gt;Hib!B9,Hib!B9,IF(Scenario_data!I9 &lt;Hib!A9,Hib!A9,Scenario_data!I9))</f>
-        <v>405959606.50779802</v>
+        <v>369318949.92487359</v>
       </c>
       <c r="J22" s="7">
         <f ca="1">IF(J9&gt;Hib!B10,Hib!B10,IF(Scenario_data!J9 &lt;Hib!A10,Hib!A10,Scenario_data!J9))</f>
-        <v>419800670.41925281</v>
+        <v>386821314.01674855</v>
       </c>
       <c r="K22" s="7">
         <f ca="1">IF(K9&gt;Hib!B11,Hib!B11,IF(Scenario_data!K9 &lt;Hib!A11,Hib!A11,Scenario_data!K9))</f>
-        <v>345731100.20960015</v>
+        <v>432800370.53421861</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3870,39 +3870,39 @@
       </c>
       <c r="C23" s="7">
         <f ca="1">IF(C10&gt;Polio!B3,Polio!B3,IF(Scenario_data!C10 &lt;Polio!A3,Polio!A3,Scenario_data!C10))</f>
-        <v>657974309.62493527</v>
+        <v>783694552.35479057</v>
       </c>
       <c r="D23" s="7">
         <f ca="1">IF(D10&gt;Polio!B4,Polio!B4,IF(Scenario_data!D10 &lt;Polio!A4,Polio!A4,Scenario_data!D10))</f>
-        <v>525451510.27095741</v>
+        <v>694558018.42390716</v>
       </c>
       <c r="E23" s="7">
         <f ca="1">IF(E10&gt;Polio!B5,Polio!B5,IF(Scenario_data!E10 &lt;Polio!A5,Polio!A5,Scenario_data!E10))</f>
-        <v>589525368.07691526</v>
+        <v>519253104.41226047</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">IF(F10&gt;Polio!B6,Polio!B6,IF(Scenario_data!F10 &lt;Polio!A6,Polio!A6,Scenario_data!F10))</f>
-        <v>825200441.98331952</v>
+        <v>846545769.72766078</v>
       </c>
       <c r="G23" s="7">
         <f ca="1">IF(G10&gt;Polio!B7,Polio!B7,IF(Scenario_data!G10 &lt;Polio!A7,Polio!A7,Scenario_data!G10))</f>
-        <v>546877499.18765593</v>
+        <v>874902965.92980409</v>
       </c>
       <c r="H23" s="7">
         <f ca="1">IF(H10&gt;Polio!B8,Polio!B8,IF(Scenario_data!H10 &lt;Polio!A8,Polio!A8,Scenario_data!H10))</f>
-        <v>789554193.32267201</v>
+        <v>951023429.01607442</v>
       </c>
       <c r="I23" s="7">
         <f ca="1">IF(I10&gt;Polio!B9,Polio!B9,IF(Scenario_data!I10 &lt;Polio!A9,Polio!A9,Scenario_data!I10))</f>
-        <v>787211889.24952233</v>
+        <v>915624691.61749613</v>
       </c>
       <c r="J23" s="7">
         <f ca="1">IF(J10&gt;Polio!B10,Polio!B10,IF(Scenario_data!J10 &lt;Polio!A10,Polio!A10,Scenario_data!J10))</f>
-        <v>1120368516.7528012</v>
+        <v>1038325781.1518395</v>
       </c>
       <c r="K23" s="7">
         <f ca="1">IF(K10&gt;Polio!B11,Polio!B11,IF(Scenario_data!K10 &lt;Polio!A11,Polio!A11,Scenario_data!K10))</f>
-        <v>679667475.8336184</v>
+        <v>898968400.15119553</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B24" s="7">
         <f ca="1">IF(B11&gt;HPV!B2,HPV!B2,IF(Scenario_data!B11 &lt;HPV!A2,HPV!A2,Scenario_data!B11))</f>
-        <v>31963266.345840931</v>
+        <v>25915770.51731832</v>
       </c>
       <c r="C24" s="7">
         <f ca="1">IF(C11&gt;HPV!B3,HPV!B3,IF(Scenario_data!C11 &lt;HPV!A3,HPV!A3,Scenario_data!C11))</f>
@@ -3919,35 +3919,35 @@
       </c>
       <c r="D24" s="7">
         <f ca="1">IF(D11&gt;HPV!B4,HPV!B4,IF(Scenario_data!D11 &lt;HPV!A4,HPV!A4,Scenario_data!D11))</f>
-        <v>38250600.375207432</v>
+        <v>35258738.193920977</v>
       </c>
       <c r="E24" s="7">
         <f ca="1">IF(E11&gt;HPV!B5,HPV!B5,IF(Scenario_data!E11 &lt;HPV!A5,HPV!A5,Scenario_data!E11))</f>
-        <v>48122185.881140113</v>
+        <v>39200401.038449273</v>
       </c>
       <c r="F24" s="7">
         <f ca="1">IF(F11&gt;HPV!B6,HPV!B6,IF(Scenario_data!F11 &lt;HPV!A6,HPV!A6,Scenario_data!F11))</f>
-        <v>47653519.512356326</v>
+        <v>47265943.538656689</v>
       </c>
       <c r="G24" s="7">
         <f ca="1">IF(G11&gt;HPV!B7,HPV!B7,IF(Scenario_data!G11 &lt;HPV!A7,HPV!A7,Scenario_data!G11))</f>
-        <v>61292965.407283232</v>
+        <v>59430649.707607023</v>
       </c>
       <c r="H24" s="7">
         <f ca="1">IF(H11&gt;HPV!B8,HPV!B8,IF(Scenario_data!H11 &lt;HPV!A8,HPV!A8,Scenario_data!H11))</f>
-        <v>78042264.65959689</v>
+        <v>64565628.185461171</v>
       </c>
       <c r="I24" s="7">
         <f ca="1">IF(I11&gt;HPV!B9,HPV!B9,IF(Scenario_data!I11 &lt;HPV!A9,HPV!A9,Scenario_data!I11))</f>
-        <v>74149519.026301503</v>
+        <v>76221504.649861902</v>
       </c>
       <c r="J24" s="7">
         <f ca="1">IF(J11&gt;HPV!B10,HPV!B10,IF(Scenario_data!J11 &lt;HPV!A10,HPV!A10,Scenario_data!J11))</f>
-        <v>81327848.355241328</v>
+        <v>76400904.950654998</v>
       </c>
       <c r="K24" s="7">
         <f ca="1">IF(K11&gt;HPV!B11,HPV!B11,IF(Scenario_data!K11 &lt;HPV!A11,HPV!A11,Scenario_data!K11))</f>
-        <v>96041229.237888366</v>
+        <v>92858989.55012843</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -3956,43 +3956,43 @@
       </c>
       <c r="B25" s="7">
         <f ca="1">IF(B12&gt;Rotavirus!B2,Rotavirus!B2,IF(Scenario_data!B12 &lt;Rotavirus!A2,Rotavirus!A2,Scenario_data!B12))</f>
-        <v>151905241.58038071</v>
+        <v>239577204.00124341</v>
       </c>
       <c r="C25" s="7">
         <f ca="1">IF(C12&gt;Rotavirus!B3,Rotavirus!B3,IF(Scenario_data!C12 &lt;Rotavirus!A3,Rotavirus!A3,Scenario_data!C12))</f>
-        <v>184158506.34682065</v>
+        <v>269501978.84332263</v>
       </c>
       <c r="D25" s="7">
         <f ca="1">IF(D12&gt;Rotavirus!B4,Rotavirus!B4,IF(Scenario_data!D12 &lt;Rotavirus!A4,Rotavirus!A4,Scenario_data!D12))</f>
-        <v>114045264.6782148</v>
+        <v>286864851.98515236</v>
       </c>
       <c r="E25" s="7">
         <f ca="1">IF(E12&gt;Rotavirus!B5,Rotavirus!B5,IF(Scenario_data!E12 &lt;Rotavirus!A5,Rotavirus!A5,Scenario_data!E12))</f>
-        <v>345071647.16502643</v>
+        <v>136881744.54928535</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">IF(F12&gt;Rotavirus!B6,Rotavirus!B6,IF(Scenario_data!F12 &lt;Rotavirus!A6,Rotavirus!A6,Scenario_data!F12))</f>
-        <v>220278680.87787583</v>
+        <v>218169265.00123906</v>
       </c>
       <c r="G25" s="7">
         <f ca="1">IF(G12&gt;Rotavirus!B7,Rotavirus!B7,IF(Scenario_data!G12 &lt;Rotavirus!A7,Rotavirus!A7,Scenario_data!G12))</f>
-        <v>446059995.10940337</v>
+        <v>335530973.63952714</v>
       </c>
       <c r="H25" s="7">
         <f ca="1">IF(H12&gt;Rotavirus!B8,Rotavirus!B8,IF(Scenario_data!H12 &lt;Rotavirus!A8,Rotavirus!A8,Scenario_data!H12))</f>
-        <v>256427774.78029674</v>
+        <v>281247690.38399482</v>
       </c>
       <c r="I25" s="7">
         <f ca="1">IF(I12&gt;Rotavirus!B9,Rotavirus!B9,IF(Scenario_data!I12 &lt;Rotavirus!A9,Rotavirus!A9,Scenario_data!I12))</f>
-        <v>413848784.27904564</v>
+        <v>316967212.40048289</v>
       </c>
       <c r="J25" s="7">
         <f ca="1">IF(J12&gt;Rotavirus!B10,Rotavirus!B10,IF(Scenario_data!J12 &lt;Rotavirus!A10,Rotavirus!A10,Scenario_data!J12))</f>
-        <v>543185133.04546654</v>
+        <v>896373650.61798525</v>
       </c>
       <c r="K25" s="7">
         <f ca="1">IF(K12&gt;Rotavirus!B11,Rotavirus!B11,IF(Scenario_data!K12 &lt;Rotavirus!A11,Rotavirus!A11,Scenario_data!K12))</f>
-        <v>542245098.33165169</v>
+        <v>694368986.98709249</v>
       </c>
       <c r="M25" s="4"/>
     </row>
@@ -4006,39 +4006,39 @@
       </c>
       <c r="C26" s="7">
         <f ca="1">IF(C13&gt;PCV!B3,PCV!B3,IF(Scenario_data!C13 &lt;PCV!A3,PCV!A3,Scenario_data!C13))</f>
-        <v>299613342.8843587</v>
+        <v>303936532.15251517</v>
       </c>
       <c r="D26" s="7">
         <f ca="1">IF(D13&gt;PCV!B4,PCV!B4,IF(Scenario_data!D13 &lt;PCV!A4,PCV!A4,Scenario_data!D13))</f>
-        <v>363423456.81929737</v>
+        <v>200898755.51546949</v>
       </c>
       <c r="E26" s="7">
         <f ca="1">IF(E13&gt;PCV!B5,PCV!B5,IF(Scenario_data!E13 &lt;PCV!A5,PCV!A5,Scenario_data!E13))</f>
-        <v>431025210.27462173</v>
+        <v>407327762.47830319</v>
       </c>
       <c r="F26" s="7">
         <f ca="1">IF(F13&gt;PCV!B6,PCV!B6,IF(Scenario_data!F13 &lt;PCV!A6,PCV!A6,Scenario_data!F13))</f>
-        <v>374903871.96941876</v>
+        <v>237877147.95639929</v>
       </c>
       <c r="G26" s="7">
         <f ca="1">IF(G13&gt;PCV!B7,PCV!B7,IF(Scenario_data!G13 &lt;PCV!A7,PCV!A7,Scenario_data!G13))</f>
-        <v>315754043.89689839</v>
+        <v>439507439.59369993</v>
       </c>
       <c r="H26" s="7">
         <f ca="1">IF(H13&gt;PCV!B8,PCV!B8,IF(Scenario_data!H13 &lt;PCV!A8,PCV!A8,Scenario_data!H13))</f>
-        <v>671941120.10131812</v>
+        <v>166480198.96793035</v>
       </c>
       <c r="I26" s="7">
         <f ca="1">IF(I13&gt;PCV!B9,PCV!B9,IF(Scenario_data!I13 &lt;PCV!A9,PCV!A9,Scenario_data!I13))</f>
-        <v>411655009.81450933</v>
+        <v>415297688.68271244</v>
       </c>
       <c r="J26" s="7">
         <f ca="1">IF(J13&gt;PCV!B10,PCV!B10,IF(Scenario_data!J13 &lt;PCV!A10,PCV!A10,Scenario_data!J13))</f>
-        <v>509524028.94588882</v>
+        <v>664164889.69489038</v>
       </c>
       <c r="K26" s="7">
         <f ca="1">IF(K13&gt;PCV!B11,PCV!B11,IF(Scenario_data!K13 &lt;PCV!A11,PCV!A11,Scenario_data!K13))</f>
-        <v>648953792.91621602</v>
+        <v>327661585.79673731</v>
       </c>
       <c r="M26" s="4"/>
     </row>
